--- a/金.xlsx
+++ b/金.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/27abbb25ad5a6e64/デスクトップ/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{40EF84B5-BF6C-4D0C-A40C-A1B86882DE4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C24A8804-23A1-403A-B0B4-8DF289B2B44C}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="13_ncr:1_{40EF84B5-BF6C-4D0C-A40C-A1B86882DE4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{791925FB-C737-48BD-B5EA-A117CBA724EE}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{FD74F80A-37BC-47A0-A399-880DAA7CC047}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FD74F80A-37BC-47A0-A399-880DAA7CC047}"/>
   </bookViews>
   <sheets>
     <sheet name="株" sheetId="2" r:id="rId1"/>
@@ -28,8 +28,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -37,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>BTC</t>
     <phoneticPr fontId="2"/>
@@ -209,13 +207,6 @@
   </si>
   <si>
     <t>INPEX</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>前日比</t>
-    <rPh sb="0" eb="3">
-      <t>ゼンジツヒ</t>
-    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -741,7 +732,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA07BF4A-A4CE-4FFC-B4F6-7CDAE557D8B1}">
-  <dimension ref="B3:L14"/>
+  <dimension ref="B6:L14"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="23.9140625" bestFit="1" customWidth="1"/>
@@ -751,57 +742,6 @@
     <col min="11" max="11" width="10.08203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="D3">
-        <f>SUM(D7:D14)</f>
-        <v>218980</v>
-      </c>
-      <c r="E3">
-        <f>SUM(E7:E11)</f>
-        <v>5596</v>
-      </c>
-      <c r="F3">
-        <f>SUM(F7:F14)</f>
-        <v>220952</v>
-      </c>
-      <c r="G3">
-        <f>SUM(G7:G11)</f>
-        <v>7568</v>
-      </c>
-      <c r="H3">
-        <f>SUM(H7:H14)</f>
-        <v>220952</v>
-      </c>
-      <c r="I3">
-        <f>SUM(I7:I11)</f>
-        <v>54566</v>
-      </c>
-      <c r="K3">
-        <f>SUM(K7:K14)</f>
-        <v>215355</v>
-      </c>
-      <c r="L3">
-        <f>SUM(L7:L13)</f>
-        <v>49209</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F4">
-        <f>F3-D3</f>
-        <v>1972</v>
-      </c>
-      <c r="H4">
-        <f>H3-F3</f>
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <f>K3-H3</f>
-        <v>-5597</v>
-      </c>
-    </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="C6" t="s">
         <v>33</v>
@@ -955,7 +895,7 @@
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C12">
         <v>26000</v>
@@ -973,7 +913,7 @@
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C13">
         <v>4650</v>
@@ -1009,10 +949,6 @@
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="D3 F3 H3" formulaRange="1"/>
-    <ignoredError sqref="E3 G3" formula="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -1455,11 +1391,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="469bfeae-8ea4-4f0e-88a2-b2c207af2e5c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1690,27 +1627,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="469bfeae-8ea4-4f0e-88a2-b2c207af2e5c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60A779F8-2C2F-40E9-93EB-127FC654BC5D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4B7FDFE-677C-49BA-A7AE-5C5B31AEB5CE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="469bfeae-8ea4-4f0e-88a2-b2c207af2e5c"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="148aecd1-c53e-46c5-b0db-965c0be3f40f"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1735,9 +1662,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4B7FDFE-677C-49BA-A7AE-5C5B31AEB5CE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60A779F8-2C2F-40E9-93EB-127FC654BC5D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="469bfeae-8ea4-4f0e-88a2-b2c207af2e5c"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="148aecd1-c53e-46c5-b0db-965c0be3f40f"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>